--- a/summary output/sample_size_table(31july2025).xlsx
+++ b/summary output/sample_size_table(31july2025).xlsx
@@ -351,55 +351,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>forest_type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>trmt</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>brush</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>harvest</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>trmt</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>brush</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>plot_count</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>n_hdwd</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>6_6</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D2">
+      <c r="E2">
         <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6_6</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,22 +419,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>20</v>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>decker</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6_6</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>protected</t>
+          <t>control</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -432,34 +447,44 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D4">
-        <v>30</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>gas_line</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6_6</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>protected</t>
+          <t>control</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>30</v>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sta_rd</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6_9</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,17 +494,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D6">
+          <t>u</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6_6</t>
+        </is>
+      </c>
+      <c r="E6">
         <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6_9</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -492,34 +522,44 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D7">
-        <v>20</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>fairfield_a6</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6_9</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>protected</t>
+          <t>control</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>20</v>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>goundry_a17</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6_9</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -529,17 +569,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="D9">
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6_6</t>
+        </is>
+      </c>
+      <c r="E9">
         <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>campridge</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -552,14 +597,19 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D10">
-        <v>94</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>decker</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>circle</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -572,39 +622,49 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D11">
-        <v>24</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>gas_line</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>danby_block_2</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>protected</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>21</v>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>recknagel_north</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>decker</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>protected</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -612,14 +672,19 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D13">
-        <v>15</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sta_rd</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>decker</t>
+          <t>n_hdwd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -629,17 +694,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>37</v>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6_6</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fairfield_a5</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -652,14 +722,19 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D15">
-        <v>21</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6_9</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fairfield_a6</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -669,17 +744,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>10</v>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>fairfield_a5</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gas_line</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -692,19 +772,24 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D17">
-        <v>17</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>recknagel</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gas_line</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>protected</t>
+          <t>control</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -712,14 +797,19 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D18">
-        <v>77</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>red_pine</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>goundry_a17</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -732,14 +822,19 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D19">
-        <v>14</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6_9</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>recknagel</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -749,17 +844,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>32</v>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>danby_block_2</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>recknagel</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -772,14 +872,19 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D21">
-        <v>38</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6_9</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>recknagel_north</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -792,19 +897,24 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D22">
-        <v>15</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>campridge</t>
+        </is>
+      </c>
+      <c r="E22">
+        <v>94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>red_pine</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>protected</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -812,14 +922,19 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D23">
-        <v>29</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="E23">
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>red_pine</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -832,19 +947,24 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D24">
-        <v>28</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>recknagel</t>
+        </is>
+      </c>
+      <c r="E24">
+        <v>38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sta_rd</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>protected</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -852,14 +972,19 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D25">
-        <v>34</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>red_pine</t>
+        </is>
+      </c>
+      <c r="E25">
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sta_rd</t>
+          <t>oak_hdwd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -869,11 +994,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>61</v>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6_9</t>
+        </is>
+      </c>
+      <c r="E26">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
